--- a/docs/downloads/05/tbl_agri_equip_marovoay_bepako.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_marovoay_bepako.xlsx
@@ -436,12 +436,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -508,12 +496,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +508,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -580,12 +556,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -634,12 +604,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -670,12 +634,6 @@
           <t>Houe</t>
         </is>
       </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +646,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -724,12 +676,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +688,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -827,12 +767,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -845,12 +779,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -881,12 +809,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -917,12 +839,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -935,12 +851,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -989,12 +899,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1025,12 +929,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1097,12 +995,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1151,12 +1043,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1187,12 +1073,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1205,12 +1085,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1223,12 +1097,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1241,12 +1109,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1277,12 +1139,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1312,12 +1168,6 @@
         <is>
           <t>Tracteur</t>
         </is>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
